--- a/demo/asteria/sources/governance/control_library.xlsx
+++ b/demo/asteria/sources/governance/control_library.xlsx
@@ -346,6 +346,1006 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P2P-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A vendor in pending status cannot be paid</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AST-R-P2P</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Per payment</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>COSO:CA-3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P2P-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Payment runs above EUR 250,000 are approved by the CFO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AST-R-P2P</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Per run</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COSO:CA-3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLA-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer response commitments are measured against the contract in force</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AST-R-SLA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Per incident</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.20</t>
+        </is>
+      </c>
+      <c r="H11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLA-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Contract amendments are reflected in operational configuration within ten business days</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AST-R-CONTRACT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gc@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Per amendment</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.20</t>
+        </is>
+      </c>
+      <c r="H12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IAM-03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Directory accounts are created only from an approved joiner record</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AST-R-IAM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Per joiner</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.16</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IAM-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Service accounts have a named human owner and rotated credentials</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AST-R-IAM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.17</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAM-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Break-glass access is time-bound and reviewed within one business day</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AST-R-PAM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Per use</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCM-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Branch protection is enabled on every repository that deploys to production</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AST-R-SCM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.32</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCM-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deployments are traceable to a merged, reviewed commit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AST-R-SDLC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Per deployment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.31</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VULN-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Critical vulnerabilities on internet-facing systems are remediated within seven days</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AST-R-VULN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Corrective</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.8</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VULN-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A build with an unremediated critical vulnerability does not deploy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AST-R-VULN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Per build</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.8</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LOG-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Administrative activity is logged and retained for 400 days</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AST-R-LOG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOG-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Log storage is write-once and not alterable by the principals it records</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AST-R-LOG</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KEY-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Key material is held in the managed key service and rotated annually</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AST-R-KEY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ciso@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.24</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KEY-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No secret is committed to source control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AST-R-KEY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Per commit</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.24</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BCP-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Restoration from backup is tested at least annually</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AST-R-BACKUP</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.13</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BCP-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A simulated P1 exercise is run twice a year</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AST-R-BCP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Half-yearly</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.29</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DPA-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Transfer of personal data outside the EEA has a documented basis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AST-R-DPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>dpo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Per transfer</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GDPR:Ch.V</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DPA-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sub-processor additions are notified 30 days in advance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AST-R-DPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>dpo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Per addition</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>GDPR:Art.28</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEG-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The requester of a purchase may not approve it</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AST-R-SEG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Per purchase</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>COSO:CA-3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SEG-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A developer may not approve their own change</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AST-R-SEG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>cto@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Per change</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ISO27001:A.8.32</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pre-employment screening completes before the start date</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AST-R-PAYROLL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>chro@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Per joiner</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ISO27001:A.6.1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HR-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Payroll changes are reconciled to the workforce roster monthly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AST-R-PAYROLL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>chro@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>COSO:CA-3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VEN-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A supplier with access to restricted data is reassessed annually</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AST-R-VENDOR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ISO27001:A.5.22</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>